--- a/output/assembly/bom/Desk_controller-bom.xlsx
+++ b/output/assembly/bom/Desk_controller-bom.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="250">
   <si>
     <t>Row</t>
   </si>
@@ -47,6 +47,12 @@
     <t>Datasheet</t>
   </si>
   <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Manufacturer Part Number</t>
+  </si>
+  <si>
     <t>Assy</t>
   </si>
   <si>
@@ -59,64 +65,646 @@
     <t>Field5</t>
   </si>
   <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>Manufacturer Part Number</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
+    <t>Unpolarized capacitor</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C10 C14</t>
+  </si>
+  <si>
+    <t>22p</t>
+  </si>
+  <si>
+    <t>C_0603_1608Metric_Pad1.08x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>AC0603JRNPO9BN220</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>33p</t>
+  </si>
+  <si>
+    <t>AC0603JRNPO9BN330</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>C7 C8 C21 C22 C23</t>
+  </si>
+  <si>
+    <t>1n</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>AC0603KRX7R9BB102</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>C3 C5 C26 C27</t>
+  </si>
+  <si>
+    <t>10n</t>
+  </si>
+  <si>
+    <t>AC0603KRX7R9BB103</t>
+  </si>
+  <si>
+    <t>C1 C6 C9 C13 C19 C20 C25</t>
+  </si>
+  <si>
+    <t>100n</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>AC0603KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>C11 C16</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>AC0603KRX7R7BB105</t>
+  </si>
+  <si>
+    <t>C2 C4</t>
+  </si>
+  <si>
+    <t>4.7u</t>
+  </si>
+  <si>
+    <t>C_1206_3216Metric_Pad1.33x1.80mm_HandSolder</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
+    <t>C1206C475K5RACAUTO</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>C15 C17 C18</t>
+  </si>
+  <si>
+    <t>22u</t>
+  </si>
+  <si>
+    <t>C_1210_3225Metric_Pad1.33x2.70mm_HandSolder</t>
+  </si>
+  <si>
+    <t>TAIYO YUDEN</t>
+  </si>
+  <si>
+    <t>MCAST32MSB7226KPNA01</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Polarized capacitor</t>
+  </si>
+  <si>
+    <t>C_Polarized</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>220u</t>
+  </si>
+  <si>
+    <t>CP_Elec_10x10</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>EEE-FK1H221P</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>BAV99 High-speed switching diodes, SOT-23</t>
+  </si>
+  <si>
+    <t>BAV99</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>https://assets.nexperia.com/documents/data-sheet/BAV99_SER.pdf</t>
+  </si>
+  <si>
+    <t>Diodes Inc</t>
+  </si>
+  <si>
+    <t>BAV99Q-7-F</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Generic connector, single row, 01x04, script generated</t>
+  </si>
+  <si>
+    <t>Conn_01x04_Pin</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>01x04 socket</t>
+  </si>
+  <si>
+    <t>PinSocket_1x04_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Generic connector, single row, 01x14, script generated</t>
+  </si>
+  <si>
+    <t>Conn_01x14_Pin</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>01x14 socket</t>
+  </si>
+  <si>
+    <t>PinSocket_1x14_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>B4B XH A</t>
+  </si>
+  <si>
+    <t>JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Generic connector, single row, 01x06, script generated</t>
+  </si>
+  <si>
+    <t>Conn_01x06_Pin</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>B6B XH A</t>
+  </si>
+  <si>
+    <t>JST_XH_B6B-XH-A_1x06_P2.50mm_Vertical</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>DC_barrel_assy</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>DC barrel assy</t>
+  </si>
+  <si>
+    <t>Dell_barrel_assy</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Dell_DC_barrel_jack</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>Dell DC jack</t>
+  </si>
+  <si>
+    <t>Dell</t>
+  </si>
+  <si>
+    <t>Barrel jack</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Generic connector, double row, 02x05, odd/even pin numbering scheme (row 1 odd numbers, row 2 even numbers), script generated (kicad-library-utils/schlib/autogen/connector/)</t>
+  </si>
+  <si>
+    <t>Conn_02x05_Odd_Even</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>HX JN1.27-2x5 WZ H4.9</t>
+  </si>
+  <si>
+    <t>JN1.27-2x5 WZ H4.9</t>
+  </si>
+  <si>
+    <t>Hanxia</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/IDC-Connectors_hanxia-HX-JN1-27-2x5-WZ-H4-9_C42372551.html?s_z=n_JILN%2520321010SG0ABK00A01</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>USB 2.0-only 16P Type-C Receptacle connector</t>
+  </si>
+  <si>
+    <t>USB_C_Receptacle_USB2.0_16P</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>USB_C_socket_16P_vertical</t>
+  </si>
+  <si>
+    <t>https://www.usb.org/sites/default/files/documents/usb_type-c.zip</t>
+  </si>
+  <si>
+    <t>ChengHaoRan</t>
+  </si>
+  <si>
+    <t>TFKH5-16L4CC-65</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>JP4 JP5 JP7 JP14 JP19</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>R_1206_3216Metric_Pad1.30x1.75mm_HandSolder</t>
+  </si>
+  <si>
+    <t>Hand cut wire</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>JP18 JP22</t>
+  </si>
+  <si>
+    <t>R_Axial_DIN0204_L3.6mm_D1.6mm_P7.62mm_Horizontal</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>JP6 JP20</t>
+  </si>
+  <si>
+    <t>R_0603_1608Metric_Pad0.98x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>RC0603JR-130RP</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>JP23</t>
+  </si>
+  <si>
+    <t>Wire_9.603mm</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>JP24</t>
+  </si>
+  <si>
+    <t>Wire_6.310mm</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>JP25</t>
+  </si>
+  <si>
+    <t>Wire_9.532mm</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>JP26</t>
+  </si>
+  <si>
+    <t>Wire_6.853x8.890mm</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>JP9</t>
+  </si>
+  <si>
+    <t>R_Axial_DIN0204_L3.6mm_D1.6mm_P5.08mm_Horizontal</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Inductor</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>10u</t>
+  </si>
+  <si>
+    <t>L_Bourns_SRP6540</t>
+  </si>
+  <si>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>SRP6540-100M</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>Resistor</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>R_0603_1608Metric_Pad0.98x0.95mm_HandSolder</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>820</t>
+  </si>
+  <si>
+    <t>YAGEO</t>
+  </si>
+  <si>
+    <t>AC0603FR-07820RL</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R4 R5 R10 R12 R13</t>
+  </si>
+  <si>
+    <t>2k2</t>
+  </si>
+  <si>
+    <t>AC0603FR-072K2L</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R14 R15</t>
+  </si>
+  <si>
+    <t>5k1</t>
+  </si>
+  <si>
+    <t>AC0603FR-075K1L</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R1 R2 R7 R8 R9</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>AC0603FR-0710KL</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>23.2k</t>
+  </si>
+  <si>
+    <t>AC0603FR-0723K2L</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
   <si>
     <t>R3</t>
   </si>
   <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>300</t>
+    <t>64.9k</t>
+  </si>
+  <si>
+    <t>AC0603FR-0764K9L</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>TFT_2.8_IN_320x240</t>
+  </si>
+  <si>
+    <t>TFT1</t>
+  </si>
+  <si>
+    <t>TFT_2.4in_320x240</t>
+  </si>
+  <si>
+    <t>Display_240x320_ILI9341_2.4in_no_pads</t>
+  </si>
+  <si>
+    <t>TENSTAR ROBOT</t>
+  </si>
+  <si>
+    <t>ILI9341_320x240</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>LMR380x0</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>LMR38020</t>
+  </si>
+  <si>
+    <t>Texas_HSOP-8-1EP_3.9x4.9mm_P1.27mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>Texas instruments</t>
+  </si>
+  <si>
+    <t>LMR38020FDDAR</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>STMicroelectronics Arm Cortex-M4 MCU, 64KB flash, 32KB RAM, 170 MHz, 1.71-3.6V, 26 GPIO, LQFP32</t>
+  </si>
+  <si>
+    <t>STM32G431K8Tx</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>STM32G431K8T</t>
+  </si>
+  <si>
+    <t>LQFP-32_7x7mm_P0.8mm</t>
+  </si>
+  <si>
+    <t>https://www.st.com/resource/en/datasheet/stm32g431k8.pdf</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>STM32G431K8T6</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Very low capacitance ESD protection diode, 2 data-line, SOT-23-6</t>
+  </si>
+  <si>
+    <t>USBLC6-2SC6</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>https://www.st.com/resource/en/datasheet/usblc6-2.pdf</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>VNH7070</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>JEITA_SOIC-16_3.9x9.9mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Four pin crystal, GND on pins 2 and 4, small symbol</t>
+  </si>
+  <si>
+    <t>Crystal_GND24_Small</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>20 MHz</t>
+  </si>
+  <si>
+    <t>Crystal_SMD_3225-4Pin_3.2x2.5mm_HandSoldering</t>
+  </si>
+  <si>
+    <t>KYOCERA AVX</t>
+  </si>
+  <si>
+    <t>CX3225SB20000H0FLJCC</t>
   </si>
   <si>
     <t>KiBot Bill of Materials</t>
@@ -137,13 +725,13 @@
     <t>Revision:</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Date:</t>
   </si>
   <si>
-    <t>06/10/2026</t>
+    <t>18/10/2026</t>
   </si>
   <si>
     <t>KiCad Version:</t>
@@ -349,8 +937,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>16584</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1464384</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>123779</xdr:rowOff>
     </xdr:to>
@@ -676,28 +1264,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="60.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="48.7109375" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
+    <col min="6" max="6" width="53.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="14" width="22.7109375" customWidth="1"/>
-    <col min="15" max="15" width="34.7109375" customWidth="1"/>
+    <col min="9" max="9" width="60.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="15" max="15" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -714,55 +1303,55 @@
     </row>
     <row r="2" spans="1:15">
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="F2" s="3">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>232</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>233</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>39</v>
+        <v>235</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>46</v>
+        <v>242</v>
       </c>
       <c r="F4" s="3">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>236</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>237</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -770,16 +1359,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="F6" s="3">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -849,36 +1438,36 @@
         <v>20</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>16</v>
@@ -887,10 +1476,10 @@
         <v>17</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>20</v>
@@ -899,33 +1488,33 @@
         <v>15</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>16</v>
@@ -934,45 +1523,45 @@
         <v>17</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>16</v>
@@ -981,39 +1570,1684 @@
         <v>17</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="30" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="45" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="30" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="10" t="s">
+      <c r="H28" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O41" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="30" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="30" customHeight="1">
+      <c r="A45" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O47" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1037,27 +3271,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>51</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>52</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>53</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/output/assembly/bom/Desk_controller-bom.xlsx
+++ b/output/assembly/bom/Desk_controller-bom.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="249">
   <si>
     <t>Row</t>
   </si>
@@ -614,10 +614,7 @@
     <t>U1</t>
   </si>
   <si>
-    <t>LMR38020</t>
-  </si>
-  <si>
-    <t>Texas_HSOP-8-1EP_3.9x4.9mm_P1.27mm_ThermalVias</t>
+    <t>Texas_HSOP-8-1EP_3.9x4.9mm_P1.27mm_ThermalVias_w_step</t>
   </si>
   <si>
     <t>Texas instruments</t>
@@ -1272,7 +1269,7 @@
     <col min="3" max="3" width="32.7109375" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
     <col min="5" max="5" width="32.7109375" customWidth="1"/>
-    <col min="6" max="6" width="53.7109375" customWidth="1"/>
+    <col min="6" max="6" width="58.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
     <col min="9" max="9" width="60.7109375" customWidth="1"/>
@@ -1286,7 +1283,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1303,13 +1300,13 @@
     </row>
     <row r="2" spans="1:15">
       <c r="C2" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F2" s="3">
         <v>39</v>
@@ -1317,13 +1314,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="C3" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3" s="3">
         <v>72</v>
@@ -1331,13 +1328,13 @@
     </row>
     <row r="4" spans="1:15">
       <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>235</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3">
         <v>72</v>
@@ -1345,13 +1342,13 @@
     </row>
     <row r="5" spans="1:15">
       <c r="C5" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1359,13 +1356,13 @@
     </row>
     <row r="6" spans="1:15">
       <c r="C6" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F6" s="3">
         <v>72</v>
@@ -3030,10 +3027,10 @@
         <v>197</v>
       </c>
       <c r="E43" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>198</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>199</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>15</v>
@@ -3045,10 +3042,10 @@
         <v>23</v>
       </c>
       <c r="J43" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="K43" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>23</v>
@@ -3065,22 +3062,22 @@
     </row>
     <row r="44" spans="1:15" ht="30" customHeight="1">
       <c r="A44" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="C44" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="D44" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="F44" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>15</v>
@@ -3089,13 +3086,13 @@
         <v>22</v>
       </c>
       <c r="I44" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J44" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="K44" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="K44" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="L44" s="12" t="s">
         <v>23</v>
@@ -3112,22 +3109,22 @@
     </row>
     <row r="45" spans="1:15" ht="30" customHeight="1">
       <c r="A45" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="C45" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="D45" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="E45" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>214</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>215</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>15</v>
@@ -3136,13 +3133,13 @@
         <v>22</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>23</v>
@@ -3159,22 +3156,22 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="E46" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="F46" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>15</v>
@@ -3186,10 +3183,10 @@
         <v>23</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L46" s="12" t="s">
         <v>23</v>
@@ -3206,22 +3203,22 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="C47" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="D47" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="E47" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>226</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>15</v>
@@ -3233,10 +3230,10 @@
         <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="K47" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>23</v>
@@ -3271,27 +3268,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/output/assembly/bom/Desk_controller-bom.xlsx
+++ b/output/assembly/bom/Desk_controller-bom.xlsx
@@ -722,13 +722,13 @@
     <t>Revision:</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Date:</t>
   </si>
   <si>
-    <t>18/10/2026</t>
+    <t>21/10/2026</t>
   </si>
   <si>
     <t>KiCad Version:</t>
